--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monday" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tuesday" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wednesday" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thursday" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Friday" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checkouts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rooms" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Monday" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tuesday" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Wednesday" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Thursday" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Friday" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Checkouts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Rooms" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="About" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monday" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tuesday" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Wednesday" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Thursday" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Friday" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Checkouts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Rooms" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="About" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monday" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tuesday" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wednesday" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thursday" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Friday" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checkouts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rooms" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:32 UTC</t>
+          <t>2026-09-15 21:31 UTC</t>
         </is>
       </c>
     </row>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -20191,7 +20191,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:30 UTC</t>
+          <t>2026-09-15 21:32 UTC</t>
         </is>
       </c>
     </row>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -20191,7 +20191,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:31 UTC</t>
+          <t>2026-09-15 21:32 UTC</t>
         </is>
       </c>
     </row>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monday" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tuesday" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wednesday" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thursday" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Friday" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checkouts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rooms" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Monday" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tuesday" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Wednesday" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Thursday" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Friday" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Checkouts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Changes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Rooms" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="About" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20005,6 +20005,60 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AMP Week 4 Meeting</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20016,7 +20070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20070,6 +20124,44 @@
           <t>note</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>thu-3414-a-practice-1045__2026-09-17</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>thu-3414-a-practice-1045</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20191,7 +20283,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:32 UTC</t>
+          <t>2026-09-16 15:21 UTC</t>
         </is>
       </c>
     </row>
@@ -20214,7 +20306,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -20224,7 +20316,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19900,12 +19900,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>becdea78-4a21-42c6-9118-f8aaea7bc91a</t>
+          <t>07debac0-f032-4276-8c4e-92d5a1c05685</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Music Tutoring</t>
+          <t>Student Accomodation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -19915,17 +19915,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Monday; Wednesday</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19935,17 +19935,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -19954,7 +19954,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
+          <t>becdea78-4a21-42c6-9118-f8aaea7bc91a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19979,27 +19979,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -20008,56 +20008,168 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMP Week 4 Meeting</t>
+          <t>Music Tutoring</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AMP Week 4 Meeting</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dance Conference</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3400 (Choir); 3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2027-02-03</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2027-02-06</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>They will have their own volunteers monitor the rooms</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20283,7 +20395,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:21 UTC</t>
+          <t>2026-09-17 15:28 UTC</t>
         </is>
       </c>
     </row>
@@ -20306,7 +20418,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20008,12 +20008,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
+          <t>5eb408f3-a93d-4df8-a475-02f262d111df</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Music Tutoring</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -20023,37 +20023,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Charlotte Wilkins</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -20062,52 +20062,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMP Week 4 Meeting</t>
+          <t>Music Tutoring</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -20116,60 +20116,446 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AMP Week 4 Meeting</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AMP Week 8 Meeting</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AMP Composition Presentation Run-thru</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AMP Composition Presentation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20182,7 +20568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20274,6 +20660,668 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-09-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-09-29</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-10-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>thu-3400-choir-1110__2026-10-29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>thu-3400-choir-1110</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>thu-3401-band-1145__2026-10-29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>thu-3401-band-1145</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>thu-3400-choir-1110__2026-11-05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>thu-3400-choir-1110</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>thu-3401-band-1145__2026-11-05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>thu-3401-band-1145</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20395,7 +21443,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:28 UTC</t>
+          <t>2026-09-18 14:50 UTC</t>
         </is>
       </c>
     </row>
@@ -20418,7 +21466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -20428,7 +21476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20116,27 +20116,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+          <t>0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMP Week 4 Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>April Amante</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -20151,17 +20151,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -20170,17 +20170,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Week 4 Meeting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -20200,12 +20200,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -20224,17 +20224,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -20254,12 +20254,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -20278,12 +20278,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -20308,17 +20308,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -20326,22 +20326,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -20366,12 +20362,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -20386,7 +20382,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -20394,17 +20390,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20414,7 +20410,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -20424,17 +20420,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -20442,23 +20438,27 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -20478,12 +20478,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -20502,60 +20502,114 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20568,7 +20622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20702,17 +20756,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-09-29</t>
+          <t>wed-3400-choir-1415__2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20722,17 +20776,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -20740,7 +20794,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-06</t>
+          <t>tue-3414-a-practice-0945__2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -20750,7 +20804,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20778,17 +20832,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-13</t>
+          <t>wed-3400-choir-1415__2026-09-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20798,17 +20852,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -20816,7 +20870,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>tue-3414-a-practice-0945__2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20826,7 +20880,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20854,17 +20908,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>wed-3400-choir-1415__2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20874,17 +20928,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -20892,17 +20946,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20912,39 +20966,35 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>wed-3400-choir-1415__2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20954,29 +21004,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20986,7 +21032,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -21014,17 +21060,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21034,39 +21080,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21076,39 +21118,35 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21118,17 +21156,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -21136,17 +21174,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21156,35 +21194,39 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -21194,25 +21236,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -21222,7 +21268,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -21250,17 +21296,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21270,17 +21316,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -21288,40 +21334,542 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>thu-3400-choir-1110__2026-11-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>thu-3400-choir-1110</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>thu-3401-band-1145__2026-11-05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>thu-3401-band-1145</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-11-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-11-18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>tue-3414-a-practice-0945__2026-12-15</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>3414-A (Practice)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21443,7 +21991,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:50 UTC</t>
+          <t>2026-09-19 14:13 UTC</t>
         </is>
       </c>
     </row>
@@ -21466,7 +22014,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -21476,7 +22024,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20116,37 +20116,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>Tutoring</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>tutoring</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>April Amante</t>
+          <t>Valerie</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -20156,12 +20156,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -20170,52 +20170,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+          <t>53ef6b05-244d-4400-bb30-39df9747dc8f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMP Week 4 Meeting</t>
+          <t>Music Tutoring</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>tutoring</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Valerie</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -20224,27 +20224,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>April Amante</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -20254,22 +20254,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -20278,12 +20278,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Week 4 Meeting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20308,12 +20308,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -20332,17 +20332,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -20362,17 +20362,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -20380,22 +20380,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -20410,7 +20406,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -20420,17 +20416,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -20438,27 +20434,23 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20468,7 +20460,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -20478,17 +20470,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -20496,18 +20488,22 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -20522,7 +20518,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -20532,17 +20528,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -20550,66 +20546,178 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21991,7 +22099,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:13 UTC</t>
+          <t>2026-09-21 16:52 UTC</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22122,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -20730,7 +20730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20826,12 +20826,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-09-22</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -20841,40 +20841,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-09-23</t>
+          <t>tue-3414-a-practice-0945__2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20884,17 +20876,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -20902,17 +20894,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-09-29</t>
+          <t>wed-3400-choir-1415__2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20922,17 +20914,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -20940,45 +20932,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-09-30</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-06</t>
+          <t>tue-3414-a-practice-0945__2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20988,7 +20972,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -21016,7 +21000,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-07</t>
+          <t>wed-3400-choir-1415__2026-09-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -21026,7 +21010,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -21054,55 +21038,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-13</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-14</t>
+          <t>tue-3414-a-practice-0945__2026-10-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -21112,17 +21088,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -21130,17 +21106,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>wed-3400-choir-1415__2026-10-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -21150,17 +21126,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -21168,45 +21144,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-21</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -21216,7 +21184,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21244,7 +21212,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>wed-3400-choir-1415__2026-10-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -21254,7 +21222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21282,59 +21250,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+          <t>(pending)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -21344,39 +21300,35 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -21386,17 +21338,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -21404,55 +21356,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -21462,39 +21406,35 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -21504,39 +21444,35 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -21546,35 +21482,39 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -21584,73 +21524,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -21660,17 +21596,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -21678,17 +21614,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -21698,17 +21634,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -21716,17 +21652,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -21736,35 +21672,39 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -21774,63 +21714,59 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -21840,7 +21776,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -21868,7 +21804,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -21878,7 +21814,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21906,78 +21842,532 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-11-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>wed-3400-choir-1415__2026-12-16</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>wed-3400-choir-1415</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>2026-12-16</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>3400 (Choir)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22099,7 +22489,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 16:52 UTC</t>
+          <t>2026-09-22 15:27 UTC</t>
         </is>
       </c>
     </row>
@@ -22132,7 +22522,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20278,17 +20278,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+          <t>10c007c2-c79f-4fd8-a74e-9728b99ffba3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMP Week 4 Meeting</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -20313,17 +20313,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -20332,22 +20332,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>23fecadf-0679-4e79-b8f4-f9643ddde586</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Cameron Wilkins</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -20362,22 +20362,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -20386,12 +20386,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Week 4 Meeting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -20416,12 +20416,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -20440,17 +20440,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -20470,17 +20470,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -20488,22 +20488,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -20518,7 +20514,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -20528,17 +20524,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -20546,27 +20542,23 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20576,7 +20568,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -20586,17 +20578,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -20604,18 +20596,22 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -20630,7 +20626,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -20640,17 +20636,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -20658,66 +20654,178 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20730,7 +20838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21038,47 +21146,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-06</t>
+          <t>wed-3414-k-perc-1300__2026-09-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-06</t>
+          <t>thu-3414-k-perc-0945__2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -21088,17 +21204,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -21106,85 +21222,85 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-07</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
+          <t>tue-3414-a-practice-0945__2026-10-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-13</t>
+          <t>wed-3400-choir-1415__2026-10-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21194,17 +21310,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -21212,17 +21328,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-14</t>
+          <t>wed-3414-k-perc-1300__2026-10-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21232,12 +21348,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -21250,85 +21366,85 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
+          <t>thu-3414-k-perc-0945__2026-10-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-21</t>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -21338,17 +21454,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -21356,47 +21472,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
+          <t>wed-3400-choir-1415__2026-10-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>wed-3414-k-perc-1300__2026-10-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -21406,17 +21530,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -21424,17 +21548,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>thu-3414-k-perc-0945__2026-10-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -21444,17 +21568,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -21462,59 +21586,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+          <t>(pending)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -21524,69 +21636,73 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>wed-3414-k-perc-1300__2026-10-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -21596,17 +21712,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -21614,17 +21730,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>thu-3414-k-perc-0945__2026-10-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -21634,17 +21750,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -21652,59 +21768,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>(pending)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -21714,69 +21818,73 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>wed-3414-k-perc-1300__2026-10-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -21786,17 +21894,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -21804,17 +21912,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21824,65 +21932,81 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(pending)</t>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -21892,17 +22016,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -21910,85 +22034,85 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -21998,17 +22122,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -22016,17 +22140,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -22036,12 +22160,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -22054,47 +22178,59 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(pending)</t>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -22104,35 +22240,39 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22142,17 +22282,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -22160,7 +22300,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -22170,7 +22310,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -22190,7 +22330,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -22200,7 +22340,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -22228,7 +22368,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -22238,7 +22378,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -22266,47 +22406,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22316,17 +22464,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -22334,40 +22482,912 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-11-18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>wed-3400-choir-1415__2026-12-16</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>wed-3400-choir-1415</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>2026-12-16</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>3400 (Choir)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-12-17</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22489,7 +23509,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:27 UTC</t>
+          <t>2026-09-23 15:21 UTC</t>
         </is>
       </c>
     </row>
@@ -22512,7 +23532,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -22522,7 +23542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -20838,7 +20838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21040,42 +21040,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-09-29</t>
+          <t>wed-3414-k-perc-1300__2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-09-29</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -21085,40 +21093,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-09-30</t>
+          <t>tue-3414-a-practice-0945__2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -21128,17 +21128,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -21146,12 +21146,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-09-30</t>
+          <t>wed-3400-choir-1415__2026-09-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -21166,12 +21166,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -21184,17 +21184,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-01</t>
+          <t>wed-3414-k-perc-1300__2026-09-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -21222,42 +21222,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-06</t>
+          <t>thu-3414-k-perc-0945__2026-10-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-06</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -21267,40 +21275,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-07</t>
+          <t>tue-3414-a-practice-0945__2026-10-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21310,17 +21310,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -21328,12 +21328,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-07</t>
+          <t>wed-3400-choir-1415__2026-10-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -21348,12 +21348,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -21366,17 +21366,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-08</t>
+          <t>wed-3414-k-perc-1300__2026-10-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21391,12 +21391,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -21404,42 +21404,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
+          <t>thu-3414-k-perc-0945__2026-10-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-13</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -21449,40 +21457,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-14</t>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21492,17 +21492,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -21510,12 +21510,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-14</t>
+          <t>wed-3400-choir-1415__2026-10-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -21530,12 +21530,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -21548,17 +21548,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-15</t>
+          <t>wed-3414-k-perc-1300__2026-10-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -21573,12 +21573,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -21586,42 +21586,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
+          <t>thu-3414-k-perc-0945__2026-10-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -21631,40 +21639,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-21</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21674,17 +21674,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -21692,12 +21692,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-21</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -21712,12 +21712,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -21730,17 +21730,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-22</t>
+          <t>wed-3414-k-perc-1300__2026-10-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -21755,12 +21755,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -21768,42 +21768,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
+          <t>thu-3414-k-perc-0945__2026-10-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -21813,40 +21821,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -21856,17 +21856,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -21874,12 +21874,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-28</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -21894,12 +21894,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -21912,17 +21912,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>wed-3414-k-perc-1300__2026-10-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21932,34 +21932,30 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -21974,12 +21970,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -21989,19 +21985,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-29</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -22016,12 +22012,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -22029,47 +22025,59 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -22079,40 +22087,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -22122,17 +22122,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -22140,12 +22140,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-04</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -22160,12 +22160,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -22178,17 +22178,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -22198,34 +22198,30 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -22240,12 +22236,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -22255,19 +22251,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-05</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -22282,12 +22278,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -22295,47 +22291,59 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -22345,40 +22353,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -22388,17 +22388,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -22406,12 +22406,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -22426,12 +22426,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -22444,17 +22444,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22469,12 +22469,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -22482,42 +22482,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -22527,40 +22535,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -22570,17 +22570,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -22588,12 +22588,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -22626,17 +22626,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -22651,12 +22651,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -22664,42 +22664,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -22709,40 +22717,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -22752,17 +22752,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -22770,12 +22770,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>wed-3400-choir-1415__2026-11-25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -22790,12 +22790,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -22808,17 +22808,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -22833,12 +22833,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -22846,42 +22846,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -22891,40 +22899,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -22934,17 +22934,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -22952,12 +22952,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>wed-3400-choir-1415__2026-12-02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -22972,12 +22972,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -22990,17 +22990,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -23015,12 +23015,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -23028,42 +23028,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -23073,40 +23081,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -23116,17 +23116,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -23134,12 +23134,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>wed-3400-choir-1415__2026-12-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -23154,12 +23154,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -23172,17 +23172,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -23197,12 +23197,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -23210,42 +23210,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -23255,40 +23263,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -23298,17 +23298,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -23316,12 +23316,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>wed-3400-choir-1415__2026-12-16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -23336,12 +23336,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -23354,40 +23354,78 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>thu-3414-k-perc-0945__2026-12-17</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23509,7 +23547,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:21 UTC</t>
+          <t>2026-09-24 15:45 UTC</t>
         </is>
       </c>
     </row>
@@ -23542,7 +23580,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20357,7 +20357,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20386,12 +20386,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+          <t>5d0d245e-af1e-46cc-bd7a-c220cf7938f1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMP Week 4 Meeting</t>
+          <t>AMP Transfer Workshop</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -20426,12 +20426,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -20440,17 +20440,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Week 4 Meeting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -20470,12 +20470,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -20494,12 +20494,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>0f43e932-7e74-4c7e-bcc2-e4e49e550f24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Transfer Workshop</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -20514,7 +20514,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -20524,22 +20524,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -20548,17 +20548,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20568,7 +20568,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -20578,17 +20578,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -20596,22 +20596,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -20626,7 +20622,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -20636,17 +20632,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -20654,27 +20650,23 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -20684,7 +20676,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -20694,17 +20686,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -20712,18 +20704,22 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -20738,7 +20734,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -20748,17 +20744,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -20766,66 +20762,178 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20838,7 +20946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22338,257 +22446,205 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -22598,7 +22654,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -22626,7 +22682,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -22636,7 +22692,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -22664,305 +22720,241 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -22972,17 +22964,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -22990,55 +22982,43 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -23048,17 +23028,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -23066,85 +23046,81 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -23154,17 +23130,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -23172,260 +23148,1406 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>thu-3414-k-perc-0945__2026-12-17</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23547,7 +24669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:45 UTC</t>
+          <t>2026-09-25 15:45 UTC</t>
         </is>
       </c>
     </row>
@@ -23570,7 +24692,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -23580,7 +24702,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -20946,7 +20946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21186,189 +21186,137 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-09-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-09-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-09-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-09-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-09-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-09-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-09-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-06</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-09-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -21378,7 +21326,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21398,7 +21346,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-06</t>
+          <t>tue-3414-a-practice-0945__2026-09-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -21408,7 +21356,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21436,55 +21384,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-09-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-07</t>
+          <t>wed-3400-choir-1415__2026-09-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21494,12 +21430,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -21512,17 +21448,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-08</t>
+          <t>wed-3414-k-perc-1300__2026-09-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -21537,12 +21473,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -21550,47 +21486,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-13</t>
+          <t>thu-3414-k-perc-0945__2026-10-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21600,17 +21532,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -21618,237 +21550,177 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-21</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-21</t>
+          <t>tue-3414-a-practice-0945__2026-10-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -21858,17 +21730,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -21876,85 +21748,81 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
+          <t>wed-3400-choir-1415__2026-10-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>wed-3414-k-perc-1300__2026-10-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -21964,17 +21832,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -21982,55 +21850,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-28</t>
+          <t>thu-3414-k-perc-0945__2026-10-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -22045,12 +21901,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -22058,245 +21914,177 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>3414-B (Practice)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-04</t>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -22306,17 +22094,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -22324,59 +22112,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>wed-3400-choir-1415__2026-10-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22386,39 +22158,35 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-05</t>
+          <t>wed-3414-k-perc-1300__2026-10-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -22433,12 +22201,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -22446,7 +22214,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -22456,7 +22224,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -22472,33 +22240,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
+          <t>thu-3414-k-perc-0945__2026-10-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -22508,7 +22288,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -22524,7 +22304,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -22534,7 +22314,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22550,75 +22330,59 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -22628,7 +22392,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -22644,55 +22408,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -22702,17 +22458,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -22720,7 +22476,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -22730,7 +22486,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -22746,17 +22502,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -22766,17 +22522,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -22784,33 +22540,45 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
+          <t>wed-3414-k-perc-1300__2026-10-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -22820,7 +22588,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -22836,33 +22604,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
+          <t>thu-3414-k-perc-0945__2026-10-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -22872,7 +22652,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -22888,7 +22668,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -22898,7 +22678,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -22914,75 +22694,59 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -22992,7 +22756,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -23008,55 +22772,47 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -23066,17 +22822,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -23084,7 +22840,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -23094,7 +22850,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -23110,17 +22866,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -23130,17 +22886,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -23148,33 +22904,45 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
+          <t>wed-3414-k-perc-1300__2026-10-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -23184,7 +22952,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -23200,153 +22968,181 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -23356,7 +23152,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -23372,119 +23168,99 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -23494,17 +23270,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -23512,7 +23288,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -23522,7 +23298,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -23538,59 +23314,83 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -23600,7 +23400,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -23616,73 +23416,101 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(pending)</t>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -23692,17 +23520,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -23710,7 +23538,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -23720,7 +23548,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -23736,83 +23564,59 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -23822,7 +23626,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -23838,97 +23642,101 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -23938,7 +23746,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -23954,99 +23762,119 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -24056,17 +23884,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -24074,7 +23902,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -24084,7 +23912,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -24100,83 +23928,59 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -24186,7 +23990,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -24202,97 +24006,101 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -24302,7 +24110,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -24318,99 +24126,119 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -24420,17 +24248,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -24438,116 +24266,1406 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>thu-3414-k-perc-0945__2026-12-17</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24669,7 +25787,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:45 UTC</t>
+          <t>2026-09-26 14:55 UTC</t>
         </is>
       </c>
     </row>
@@ -24702,7 +25820,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20548,12 +20548,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>97131d93-2a09-4ad6-a366-f22a3a1f9440</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Intro to Recording - MUS 165</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -20563,37 +20563,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Mark Cross</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -20602,17 +20602,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -20632,12 +20632,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -20656,12 +20656,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -20686,17 +20686,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -20704,22 +20704,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -20744,12 +20740,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -20764,7 +20760,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -20772,17 +20768,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20792,7 +20788,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -20802,17 +20798,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -20820,23 +20816,27 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -20856,12 +20856,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -20880,60 +20880,114 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25787,7 +25841,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:55 UTC</t>
+          <t>2026-09-29 16:49 UTC</t>
         </is>
       </c>
     </row>
@@ -25810,7 +25864,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -20548,27 +20548,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>97131d93-2a09-4ad6-a366-f22a3a1f9440</t>
+          <t>0ff1d3c5-313b-4afa-b46e-282bfc532844</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intro to Recording - MUS 165</t>
+          <t>Tutoring</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>tutoring</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mark Cross</t>
+          <t>Valerie</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -20588,12 +20588,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -20602,52 +20602,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>97131d93-2a09-4ad6-a366-f22a3a1f9440</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Intro to Recording</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>class</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Mark Cross</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -20656,27 +20656,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>f1e6ed32-7372-4080-97c7-3ef02b385a1d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Byron Sleugh</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -20686,22 +20686,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -20710,17 +20710,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20730,7 +20730,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -20740,17 +20740,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -20758,22 +20758,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -20788,7 +20784,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -20798,17 +20794,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -20816,27 +20812,23 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20846,7 +20838,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -20856,17 +20848,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -20874,18 +20866,22 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -20900,7 +20896,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -20910,17 +20906,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -20928,66 +20924,178 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25841,7 +25949,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 UTC</t>
+          <t>2026-09-30 16:43 UTC</t>
         </is>
       </c>
     </row>
@@ -25864,7 +25972,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20656,27 +20656,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f1e6ed32-7372-4080-97c7-3ef02b385a1d</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Byron Sleugh</t>
+          <t>Charlotte Wilkins</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -20686,22 +20686,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -20710,17 +20710,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20730,7 +20730,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -20740,12 +20740,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -20764,12 +20764,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -20794,17 +20794,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -20812,18 +20812,22 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -20848,12 +20852,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -20868,7 +20872,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -20876,17 +20880,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20896,7 +20900,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -20906,17 +20910,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -20924,27 +20928,23 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Week 12 Meeting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -20964,12 +20964,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -20988,12 +20988,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>Dance Conference</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -21003,12 +21003,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -21018,84 +21018,30 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>They will have their own volunteers monitor the rooms</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Dance Conference</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Wendy</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>3400 (Choir); 3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>every day</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2027-02-03</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2027-02-06</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>23:59</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>They will have their own volunteers monitor the rooms</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25949,7 +25895,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:43 UTC</t>
+          <t>2026-10-01 17:18 UTC</t>
         </is>
       </c>
     </row>
@@ -25972,7 +25918,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -20656,12 +20656,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>8da3234c-c8ba-4f68-8a9b-66ea350409cc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Student Accommodation - Datis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -20671,37 +20671,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Monday; Wednesday</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -20710,17 +20710,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20730,7 +20730,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -20740,12 +20740,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -20764,12 +20764,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -20794,17 +20794,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -20812,22 +20812,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -20852,12 +20848,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -20872,7 +20868,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -20880,17 +20876,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20900,7 +20896,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -20910,17 +20906,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -20928,23 +20924,27 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -20964,12 +20964,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -20988,60 +20988,114 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25895,7 +25949,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:18 UTC</t>
+          <t>2026-10-05 19:33 UTC</t>
         </is>
       </c>
     </row>
@@ -25918,7 +25972,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20710,27 +20710,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>2a209309-7250-48f0-8971-2439d1202b66</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Sophia Reyes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -20740,22 +20740,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -20764,17 +20764,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -20794,12 +20794,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -20818,12 +20818,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -20838,7 +20838,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -20848,17 +20848,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -20866,22 +20866,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -20906,12 +20902,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -20926,7 +20922,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -20934,17 +20930,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20954,7 +20950,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -20964,17 +20960,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -20982,23 +20978,27 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -21018,12 +21018,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -21042,60 +21042,114 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21108,7 +21162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22038,12 +22092,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-08</t>
+          <t>thu-3400-choir-1110__2026-10-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -22053,56 +22107,56 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-09</t>
+          <t>thu-3414-k-perc-0945__2026-10-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -22112,7 +22166,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -22128,7 +22182,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -22138,7 +22192,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22154,7 +22208,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -22164,7 +22218,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -22180,7 +22234,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -22190,7 +22244,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -22206,12 +22260,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -22221,27 +22275,23 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-13</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -22251,61 +22301,65 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-14</t>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -22315,35 +22369,23 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-14</t>
+          <t>wed-3400-choir-1415__2026-10-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -22358,12 +22400,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -22376,38 +22418,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-15</t>
+          <t>wed-3414-k-perc-1300__2026-10-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -22417,56 +22471,56 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-16</t>
+          <t>thu-3414-k-perc-0945__2026-10-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -22476,7 +22530,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22492,7 +22546,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -22502,7 +22556,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -22518,7 +22572,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -22528,7 +22582,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -22544,7 +22598,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -22554,7 +22608,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -22570,12 +22624,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -22585,27 +22639,23 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -22615,61 +22665,65 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -22679,35 +22733,23 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-21</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -22722,12 +22764,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -22740,38 +22782,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
+          <t>wed-3414-k-perc-1300__2026-10-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -22781,56 +22835,56 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
+          <t>thu-3414-k-perc-0945__2026-10-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -22840,7 +22894,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -22856,7 +22910,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -22866,7 +22920,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -22882,7 +22936,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -22892,7 +22946,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -22908,7 +22962,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -22918,7 +22972,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -22934,12 +22988,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -22949,27 +23003,23 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -22979,61 +23029,65 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -23043,35 +23097,23 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-28</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -23086,12 +23128,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -23104,38 +23146,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
+          <t>wed-3414-k-perc-1300__2026-10-28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -23145,39 +23199,23 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -23192,12 +23230,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -23207,19 +23245,19 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-29</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -23234,12 +23272,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -23247,38 +23285,54 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -23288,7 +23342,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -23304,7 +23358,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -23314,7 +23368,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -23330,7 +23384,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -23340,7 +23394,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -23356,7 +23410,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -23366,7 +23420,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -23382,12 +23436,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -23397,27 +23451,23 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -23427,61 +23477,65 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -23491,35 +23545,23 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-04</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -23534,12 +23576,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -23552,38 +23594,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -23593,39 +23647,23 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -23640,12 +23678,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -23655,19 +23693,19 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-05</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -23682,12 +23720,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -23695,38 +23733,54 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -23736,7 +23790,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -23752,7 +23806,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -23762,7 +23816,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -23778,7 +23832,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -23788,7 +23842,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -23804,7 +23858,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -23814,7 +23868,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -23830,12 +23884,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -23845,27 +23899,23 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -23875,61 +23925,65 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -23939,35 +23993,23 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -23982,12 +24024,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -24000,38 +24042,50 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -24041,56 +24095,56 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -24100,7 +24154,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -24116,7 +24170,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -24126,7 +24180,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -24142,7 +24196,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -24152,7 +24206,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -24168,7 +24222,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -24178,7 +24232,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -24194,12 +24248,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -24209,27 +24263,23 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -24239,61 +24289,65 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -24303,35 +24357,23 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -24346,12 +24388,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -24364,38 +24406,50 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -24405,56 +24459,56 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -24464,7 +24518,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -24480,7 +24534,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -24490,7 +24544,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -24506,7 +24560,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -24516,7 +24570,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -24532,7 +24586,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -24542,7 +24596,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -24558,12 +24612,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -24573,27 +24627,23 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -24603,61 +24653,65 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -24667,35 +24721,23 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>wed-3400-choir-1415__2026-11-25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -24710,12 +24752,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -24728,38 +24770,50 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -24769,56 +24823,56 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -24828,7 +24882,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24844,7 +24898,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -24854,7 +24908,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24870,7 +24924,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -24880,7 +24934,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24896,7 +24950,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -24906,7 +24960,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24922,12 +24976,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -24937,27 +24991,23 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -24967,61 +25017,65 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -25031,35 +25085,23 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>wed-3400-choir-1415__2026-12-02</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -25074,12 +25116,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -25092,38 +25134,50 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -25133,56 +25187,56 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -25192,7 +25246,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -25208,7 +25262,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -25218,7 +25272,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -25234,7 +25288,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -25244,7 +25298,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -25260,7 +25314,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -25270,7 +25324,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -25286,12 +25340,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -25301,27 +25355,23 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -25331,61 +25381,65 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -25395,35 +25449,23 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>wed-3400-choir-1415__2026-12-09</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -25438,12 +25480,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -25456,38 +25498,50 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -25497,56 +25551,56 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -25556,7 +25610,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -25572,7 +25626,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -25582,7 +25636,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -25598,7 +25652,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -25608,7 +25662,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -25624,7 +25678,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -25634,7 +25688,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -25650,12 +25704,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -25665,27 +25719,23 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -25695,40 +25745,32 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -25738,17 +25780,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -25756,12 +25798,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>wed-3400-choir-1415__2026-12-16</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -25776,12 +25818,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -25794,40 +25836,78 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
           <t>thu-3414-k-perc-0945__2026-12-17</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25949,7 +26029,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:33 UTC</t>
+          <t>2026-10-06 17:04 UTC</t>
         </is>
       </c>
     </row>
@@ -25972,7 +26052,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -25982,7 +26062,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20710,52 +20710,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2a209309-7250-48f0-8971-2439d1202b66</t>
+          <t>bfe10a39-daf6-42c3-ba1b-6700bdf68071</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rehearsal</t>
+          <t>College Choir Sectionals</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>class</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sophia Reyes</t>
+          <t>Gaga</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -20764,27 +20764,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>2a209309-7250-48f0-8971-2439d1202b66</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Sophia Reyes</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -20794,22 +20794,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -20818,52 +20818,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Wendy Mazon</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -20872,17 +20872,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20892,7 +20892,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -20902,17 +20902,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -20920,22 +20920,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -20950,7 +20946,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -20960,17 +20956,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -20978,27 +20974,23 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21008,7 +21000,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -21018,17 +21010,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -21036,18 +21028,22 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -21062,7 +21058,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -21072,17 +21068,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -21090,66 +21086,178 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26029,7 +26137,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 17:04 UTC</t>
+          <t>2026-10-07 17:42 UTC</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26160,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20764,52 +20764,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2a209309-7250-48f0-8971-2439d1202b66</t>
+          <t>e6a31aa2-7894-4852-87bd-5b57dd0ea489</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rehearsal</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sophia Reyes</t>
+          <t>Mark Cross</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-M (Commercial)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Monday; Tuesday; Wednesday; Thursday</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -20818,52 +20818,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
+          <t>2a209309-7250-48f0-8971-2439d1202b66</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Office Hours</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wendy Mazon</t>
+          <t>Sophia Reyes</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -20872,52 +20872,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Wendy Mazon</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -20926,52 +20926,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>51aa789c-5701-46de-83dd-5154b51b00dd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Wendy Mazon</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -20980,17 +20980,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21000,7 +21000,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -21010,17 +21010,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -21028,22 +21028,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -21058,7 +21054,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -21068,17 +21064,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -21086,27 +21082,23 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -21116,7 +21108,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -21126,17 +21118,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -21144,18 +21136,22 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -21170,7 +21166,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -21180,17 +21176,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -21198,66 +21194,178 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21270,7 +21378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22174,38 +22282,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-08</t>
+          <t>wed-3424-piano-lab-1015__2026-10-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -22226,12 +22346,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-08</t>
+          <t>thu-3400-choir-1110__2026-10-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -22241,56 +22361,56 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-09</t>
+          <t>thu-3414-k-perc-0945__2026-10-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -22300,7 +22420,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22316,7 +22436,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -22326,7 +22446,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -22342,7 +22462,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -22352,7 +22472,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -22368,7 +22488,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -22378,7 +22498,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -22394,12 +22514,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -22409,27 +22529,23 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-13</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -22439,61 +22555,65 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-14</t>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -22503,35 +22623,23 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-14</t>
+          <t>wed-3400-choir-1415__2026-10-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -22546,12 +22654,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -22564,43 +22672,55 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-15</t>
+          <t>wed-3414-k-perc-1300__2026-10-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-15</t>
+          <t>wed-3424-piano-lab-1015__2026-10-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -22610,17 +22730,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -22628,7 +22748,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -22638,7 +22758,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22654,33 +22774,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-17</t>
+          <t>thu-3414-k-perc-0945__2026-10-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -22690,7 +22822,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -22706,7 +22838,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -22716,7 +22848,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -22732,7 +22864,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -22742,7 +22874,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -22758,42 +22890,38 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -22803,66 +22931,58 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-21</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -22872,17 +22992,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -22890,12 +23010,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -22905,66 +23025,66 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-22</t>
+          <t>wed-3414-k-perc-1300__2026-10-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -22979,12 +23099,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -22992,33 +23112,45 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
+          <t>wed-3424-piano-lab-1015__2026-10-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -23028,7 +23160,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -23044,33 +23176,45 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
+          <t>thu-3414-k-perc-0945__2026-10-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -23080,7 +23224,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -23096,7 +23240,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -23106,7 +23250,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -23122,75 +23266,59 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -23200,7 +23328,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -23216,55 +23344,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-28</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -23274,17 +23394,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -23292,7 +23412,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -23302,7 +23422,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -23318,17 +23438,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -23338,39 +23458,35 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>wed-3414-k-perc-1300__2026-10-28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -23380,39 +23496,35 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-29</t>
+          <t>wed-3424-piano-lab-1015__2026-10-28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -23422,17 +23534,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -23440,7 +23552,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -23450,7 +23562,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -23466,85 +23578,129 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -23554,7 +23710,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -23570,75 +23726,59 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -23648,7 +23788,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -23664,161 +23804,137 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-04</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -23828,39 +23944,35 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-05</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -23875,12 +23987,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -23888,33 +24000,45 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
+          <t>wed-3424-piano-lab-1015__2026-11-04</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -23924,7 +24048,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -23940,153 +24064,181 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -24096,7 +24248,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -24112,119 +24264,99 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -24234,17 +24366,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -24252,7 +24384,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -24262,7 +24394,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -24278,85 +24410,121 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
+          <t>wed-3424-piano-lab-1015__2026-11-11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -24366,7 +24534,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -24382,75 +24550,71 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -24460,7 +24624,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -24476,83 +24640,59 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -24562,7 +24702,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -24578,71 +24718,75 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -24652,7 +24796,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -24668,125 +24812,157 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
+          <t>wed-3424-piano-lab-1015__2026-11-18</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -24796,17 +24972,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -24814,7 +24990,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -24824,7 +25000,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -24840,83 +25016,59 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -24926,7 +25078,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -24942,97 +25094,101 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -25042,7 +25198,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -25058,229 +25214,237 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+          <t>wed-3400-choir-1415__2026-11-25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>wed-3424-piano-lab-1015__2026-11-25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -25290,7 +25454,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25306,45 +25470,33 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -25354,7 +25506,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -25370,59 +25522,75 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -25432,7 +25600,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -25448,73 +25616,93 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+          <t>wed-3400-choir-1415__2026-12-02</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>wed-3424-piano-lab-1015__2026-12-02</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -25524,17 +25712,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -25542,7 +25730,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -25552,7 +25740,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -25568,17 +25756,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -25588,17 +25776,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -25606,45 +25794,33 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -25654,7 +25830,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -25670,45 +25846,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -25718,7 +25882,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -25734,7 +25898,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -25744,7 +25908,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -25760,59 +25924,75 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -25822,7 +26002,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -25838,47 +26018,55 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>wed-3400-choir-1415__2026-12-09</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -25888,17 +26076,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -25906,17 +26094,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>wed-3424-piano-lab-1015__2026-12-09</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -25926,17 +26114,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -25944,78 +26132,416 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>wed-3424-piano-lab-1015__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>wed-3424-piano-lab-1015</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>thu-3414-k-perc-0945__2026-12-17</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26137,7 +26663,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:42 UTC</t>
+          <t>2026-10-08 17:46 UTC</t>
         </is>
       </c>
     </row>
@@ -26160,7 +26686,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -26170,7 +26696,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20872,52 +20872,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
+          <t>77a65a10-a59a-4f96-a76b-94077f9e3578</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Office Hours</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wendy Mazon</t>
+          <t>Holly Palmer</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -20926,52 +20926,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>51aa789c-5701-46de-83dd-5154b51b00dd</t>
+          <t>222a7106-bf8f-4e4c-8d02-b585a311396c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Office Hours</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wendy Mazon</t>
+          <t>Simone, Khalel, Jace, Gabriel Ortiz, Gabriel Magana</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3414-K (Perc)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>09:00</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>09:30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -20980,27 +20980,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>c242808b-916e-4faf-8cb3-31874d7f3fb2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Nicole Shaynis</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -21010,76 +21010,80 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Gabe O Gabriel M Shimone Sophia Reyes Valerie Siegler Hamta Jesse James  Nicole Sheynis</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Wendy Mazon</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -21088,75 +21092,71 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>51aa789c-5701-46de-83dd-5154b51b00dd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Wendy Mazon</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -21176,17 +21176,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -21194,27 +21194,23 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -21224,7 +21220,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -21234,12 +21230,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -21258,12 +21254,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -21278,7 +21274,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -21288,17 +21284,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -21306,66 +21302,236 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AMP Composition Presentation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21378,7 +21544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22410,33 +22576,45 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-09</t>
+          <t>thu-3423-1315__2026-10-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -22446,7 +22624,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -22462,59 +22640,79 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-11</t>
+          <t>res:222a7106-bf8f-4e4c-8d02-b585a311396c__2026-10-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:222a7106-bf8f-4e4c-8d02-b585a311396c</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3414-K (Perc)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Jace, Gabriel Ortiz, Gabriel Magana</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-12</t>
+          <t>res:c242808b-916e-4faf-8cb3-31874d7f3fb2__2026-10-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:c242808b-916e-4faf-8cb3-31874d7f3fb2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Gabe O Gabriel M Shimone Sophia Reyes Valerie Siegler Hamta Jesse James  Nicole Sheynis</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -22524,7 +22722,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -22540,75 +22738,59 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -22618,7 +22800,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -22634,55 +22816,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-14</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-14</t>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -22692,17 +22866,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -22710,12 +22884,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-10-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -22725,66 +22899,66 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-15</t>
+          <t>wed-3400-choir-1415__2026-10-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-15</t>
+          <t>wed-3414-k-perc-1300__2026-10-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -22799,12 +22973,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -22812,33 +22986,45 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-16</t>
+          <t>wed-3424-piano-lab-1015__2026-10-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -22848,7 +23034,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -22864,59 +23050,83 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-18</t>
+          <t>thu-3414-k-perc-0945__2026-10-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-19</t>
+          <t>thu-3423-1315__2026-10-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -22926,7 +23136,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -22942,75 +23152,59 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23020,7 +23214,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -23036,93 +23230,73 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-21</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-10-21</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -23132,17 +23306,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -23150,7 +23324,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -23160,7 +23334,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -23176,17 +23350,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-22</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -23196,17 +23370,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -23214,59 +23388,83 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
+          <t>wed-3414-k-perc-1300__2026-10-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
+          <t>wed-3424-piano-lab-1015__2026-10-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -23276,7 +23474,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -23292,127 +23490,135 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
+          <t>thu-3414-k-perc-0945__2026-10-22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
+          <t>thu-3423-1315__2026-10-22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -23422,7 +23628,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -23438,199 +23644,163 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-10-28</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -23640,39 +23810,35 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-29</t>
+          <t>wed-3414-k-perc-1300__2026-10-28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -23687,12 +23853,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -23700,33 +23866,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
+          <t>wed-3424-piano-lab-1015__2026-10-28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -23736,7 +23914,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -23752,153 +23930,193 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>thu-3423-1315__2026-10-29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -23908,7 +24126,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -23924,157 +24142,125 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -24084,81 +24270,61 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>3414-B (Practice)</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-05</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -24168,17 +24334,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -24186,59 +24352,83 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
+          <t>wed-3424-piano-lab-1015__2026-11-04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -24248,7 +24438,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -24264,99 +24454,139 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>3414-B (Practice)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>thu-3423-1315__2026-11-05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -24366,17 +24596,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -24384,7 +24614,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -24394,7 +24624,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -24410,121 +24640,85 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -24534,7 +24728,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -24550,71 +24744,75 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -24624,7 +24822,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -24640,125 +24838,157 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
+          <t>wed-3424-piano-lab-1015__2026-11-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -24768,17 +24998,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -24786,147 +25016,123 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
+          <t>thu-3423-1315__2026-11-12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -24936,7 +25142,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -24952,97 +25158,101 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -25052,7 +25262,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -25068,163 +25278,195 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>wed-3424-piano-lab-1015__2026-11-18</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>thu-3423-1315__2026-11-19</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -25234,17 +25476,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -25252,83 +25494,59 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -25338,7 +25556,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25354,45 +25572,33 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -25402,7 +25608,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25418,59 +25624,75 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -25480,7 +25702,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -25496,73 +25718,93 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+          <t>wed-3400-choir-1415__2026-11-25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>wed-3424-piano-lab-1015__2026-11-25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -25572,17 +25814,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -25590,7 +25832,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -25600,7 +25842,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -25616,17 +25858,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -25636,17 +25878,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -25654,17 +25896,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>thu-3423-1315__2026-11-26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -25674,17 +25916,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -25692,45 +25934,33 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -25740,7 +25970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -25756,45 +25986,33 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -25804,7 +26022,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -25820,7 +26038,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -25830,7 +26048,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -25846,59 +26064,75 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -25908,7 +26142,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -25924,47 +26158,55 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>wed-3400-choir-1415__2026-12-02</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -25974,17 +26216,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -25992,81 +26234,81 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+          <t>wed-3424-piano-lab-1015__2026-12-02</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -26081,12 +26323,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -26094,17 +26336,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-09</t>
+          <t>thu-3423-1315__2026-12-03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -26114,17 +26356,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -26132,7 +26374,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -26142,7 +26384,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -26158,45 +26400,33 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -26206,7 +26436,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -26222,7 +26452,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -26232,7 +26462,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -26248,7 +26478,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -26258,7 +26488,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -26274,99 +26504,111 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>wed-3400-choir-1415__2026-12-09</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26376,17 +26618,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -26394,17 +26636,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26414,12 +26656,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -26432,17 +26674,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>wed-3424-piano-lab-1015__2026-12-09</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26452,17 +26694,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
@@ -26470,78 +26712,492 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>thu-3423-1315__2026-12-10</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>thu-3423-1315</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>tue-3414-a-practice-0945</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>wed-3400-choir-1415</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>wed-3414-k-perc-1300</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>wed-3424-piano-lab-1015__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>wed-3424-piano-lab-1015</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
           <t>thu-3414-k-perc-0945__2026-12-17</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>thu-3423-1315__2026-12-17</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>thu-3423-1315</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26663,7 +27319,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:46 UTC</t>
+          <t>2026-10-09 17:22 UTC</t>
         </is>
       </c>
     </row>
@@ -26686,7 +27342,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -26696,7 +27352,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -21544,7 +21544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22614,12 +22614,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-09</t>
+          <t>fri-3422-1245__2026-10-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>fri-3422-1245</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -22629,23 +22629,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>res:222a7106-bf8f-4e4c-8d02-b585a311396c__2026-10-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>res:222a7106-bf8f-4e4c-8d02-b585a311396c</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -22655,39 +22667,23 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>3414-K (Perc)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Jace, Gabriel Ortiz, Gabriel Magana</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>res:c242808b-916e-4faf-8cb3-31874d7f3fb2__2026-10-09</t>
+          <t>res:222a7106-bf8f-4e4c-8d02-b585a311396c__2026-10-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>res:c242808b-916e-4faf-8cb3-31874d7f3fb2</t>
+          <t>res:222a7106-bf8f-4e4c-8d02-b585a311396c</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -22697,48 +22693,64 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3414-K (Perc)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Gabe O Gabriel M Shimone Sophia Reyes Valerie Siegler Hamta Jesse James  Nicole Sheynis</t>
+          <t>Jace, Gabriel Ortiz, Gabriel Magana</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-10</t>
+          <t>res:c242808b-916e-4faf-8cb3-31874d7f3fb2__2026-10-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:c242808b-916e-4faf-8cb3-31874d7f3fb2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Gabe O Gabriel M Shimone Sophia Reyes Valerie Siegler Hamta Jesse James  Nicole Sheynis</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -22748,7 +22760,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -22764,7 +22776,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -22774,7 +22786,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22790,7 +22802,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -22800,7 +22812,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -22816,12 +22828,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -22831,27 +22843,23 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-13</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -22861,61 +22869,65 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-14</t>
+          <t>tue-3414-a-practice-0945__2026-10-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -22925,35 +22937,23 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-14</t>
+          <t>wed-3400-choir-1415__2026-10-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -22968,12 +22968,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -22986,12 +22986,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-10-14</t>
+          <t>wed-3414-k-perc-1300__2026-10-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -23006,17 +23006,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -23024,38 +23024,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-15</t>
+          <t>wed-3424-piano-lab-1015__2026-10-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -23065,35 +23077,23 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-10-15</t>
+          <t>thu-3414-k-perc-0945__2026-10-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -23108,17 +23108,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -23126,33 +23126,45 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-16</t>
+          <t>thu-3423-1315__2026-10-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -23162,7 +23174,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -23178,7 +23190,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -23188,7 +23200,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -23204,7 +23216,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23214,7 +23226,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -23230,7 +23242,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23240,7 +23252,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -23256,12 +23268,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -23271,27 +23283,23 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -23301,61 +23309,65 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -23365,35 +23377,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-21</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -23408,12 +23408,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -23426,12 +23426,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-10-21</t>
+          <t>wed-3414-k-perc-1300__2026-10-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -23446,17 +23446,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -23464,38 +23464,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
+          <t>wed-3424-piano-lab-1015__2026-10-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -23505,35 +23517,23 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-10-22</t>
+          <t>thu-3414-k-perc-0945__2026-10-22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -23548,17 +23548,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -23566,33 +23566,45 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
+          <t>thu-3423-1315__2026-10-22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -23602,7 +23614,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -23618,7 +23630,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -23628,7 +23640,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -23644,7 +23656,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -23654,7 +23666,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -23670,7 +23682,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -23680,7 +23692,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -23696,12 +23708,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -23711,27 +23723,23 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -23741,61 +23749,65 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -23805,35 +23817,23 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-28</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -23848,12 +23848,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -23866,12 +23866,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-10-28</t>
+          <t>wed-3414-k-perc-1300__2026-10-28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -23886,17 +23886,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -23904,38 +23904,50 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
+          <t>wed-3424-piano-lab-1015__2026-10-28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -23945,39 +23957,23 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -23992,12 +23988,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -24007,19 +24003,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-29</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -24034,12 +24030,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -24047,17 +24043,21 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-10-29</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -24072,17 +24072,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -24090,33 +24090,45 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
+          <t>thu-3423-1315__2026-10-29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -24126,7 +24138,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -24142,7 +24154,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -24152,7 +24164,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -24168,7 +24180,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -24178,7 +24190,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -24194,7 +24206,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -24204,7 +24216,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -24220,12 +24232,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -24235,27 +24247,23 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -24265,61 +24273,65 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -24329,35 +24341,23 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-04</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -24372,12 +24372,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -24390,12 +24390,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-04</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -24410,17 +24410,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -24428,38 +24428,50 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
+          <t>wed-3424-piano-lab-1015__2026-11-04</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -24469,39 +24481,23 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -24516,12 +24512,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -24531,19 +24527,19 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-05</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -24558,12 +24554,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -24571,17 +24567,21 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-05</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -24596,17 +24596,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -24614,33 +24614,45 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
+          <t>thu-3423-1315__2026-11-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -24650,7 +24662,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -24666,7 +24678,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -24676,7 +24688,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -24692,7 +24704,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -24702,7 +24714,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -24718,7 +24730,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -24728,7 +24740,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -24744,12 +24756,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -24759,27 +24771,23 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -24789,61 +24797,65 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -24853,35 +24865,23 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -24896,12 +24896,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -24914,12 +24914,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-11</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -24934,17 +24934,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -24952,38 +24952,50 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
+          <t>wed-3424-piano-lab-1015__2026-11-11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -24993,35 +25005,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-12</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -25036,17 +25036,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -25054,33 +25054,45 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
+          <t>thu-3423-1315__2026-11-12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -25090,7 +25102,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -25106,7 +25118,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -25116,7 +25128,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -25132,7 +25144,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -25142,7 +25154,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -25158,7 +25170,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -25168,7 +25180,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -25184,12 +25196,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -25199,27 +25211,23 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -25229,61 +25237,65 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -25293,35 +25305,23 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -25336,12 +25336,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -25354,12 +25354,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-18</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -25374,17 +25374,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -25392,38 +25392,50 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
+          <t>wed-3424-piano-lab-1015__2026-11-18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -25433,35 +25445,23 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-19</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -25476,17 +25476,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -25494,33 +25494,45 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
+          <t>thu-3423-1315__2026-11-19</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -25530,7 +25542,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -25546,7 +25558,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -25556,7 +25568,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25572,7 +25584,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -25582,7 +25594,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25598,7 +25610,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -25608,7 +25620,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25624,12 +25636,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -25639,27 +25651,23 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -25669,61 +25677,65 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -25733,35 +25745,23 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>wed-3400-choir-1415__2026-11-25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -25776,12 +25776,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -25794,12 +25794,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-25</t>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -25814,17 +25814,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -25832,38 +25832,50 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+          <t>wed-3424-piano-lab-1015__2026-11-25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -25873,35 +25885,23 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-26</t>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -25916,17 +25916,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -25934,33 +25934,45 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+          <t>thu-3423-1315__2026-11-26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -25970,7 +25982,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -25986,7 +25998,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -25996,7 +26008,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -26012,7 +26024,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -26022,7 +26034,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -26038,7 +26050,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -26048,7 +26060,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -26064,12 +26076,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -26079,27 +26091,23 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -26109,61 +26117,65 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -26173,35 +26185,23 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>wed-3400-choir-1415__2026-12-02</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -26216,12 +26216,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -26234,12 +26234,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-02</t>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -26254,17 +26254,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -26272,38 +26272,50 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+          <t>wed-3424-piano-lab-1015__2026-12-02</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -26313,35 +26325,23 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-12-03</t>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -26356,17 +26356,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -26374,33 +26374,45 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+          <t>thu-3423-1315__2026-12-03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -26410,7 +26422,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -26426,7 +26438,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -26436,7 +26448,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -26452,7 +26464,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -26462,7 +26474,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -26478,7 +26490,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -26488,7 +26500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -26504,12 +26516,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -26519,27 +26531,23 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -26549,61 +26557,65 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -26613,35 +26625,23 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>wed-3400-choir-1415__2026-12-09</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -26656,12 +26656,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -26674,12 +26674,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-09</t>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -26694,17 +26694,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
@@ -26712,38 +26712,50 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+          <t>wed-3424-piano-lab-1015__2026-12-09</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -26753,35 +26765,23 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-12-10</t>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -26796,17 +26796,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -26814,33 +26814,45 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+          <t>thu-3423-1315__2026-12-10</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -26850,7 +26862,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -26866,7 +26878,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -26876,7 +26888,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -26892,7 +26904,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -26902,7 +26914,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -26918,7 +26930,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -26928,7 +26940,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -26944,12 +26956,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -26959,27 +26971,23 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -26989,40 +26997,32 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -27032,17 +27032,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -27050,12 +27050,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>wed-3400-choir-1415__2026-12-16</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -27070,12 +27070,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -27088,12 +27088,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-16</t>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -27108,17 +27108,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -27126,17 +27126,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-17</t>
+          <t>wed-3424-piano-lab-1015__2026-12-16</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -27146,17 +27146,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -27164,40 +27164,78 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
+          <t>thu-3414-k-perc-0945__2026-12-17</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
           <t>thu-3423-1315__2026-12-17</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>thu-3423-1315</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>3422</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27319,7 +27357,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09 17:22 UTC</t>
+          <t>2026-10-10 16:08 UTC</t>
         </is>
       </c>
     </row>
@@ -27352,7 +27390,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -20062,22 +20062,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
+          <t>d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Music Tutoring</t>
+          <t>Tutoring</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>tutoring</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Valerie</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -20087,27 +20087,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -20116,12 +20116,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>53ef6b05-244d-4400-bb30-39df9747dc8f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tutoring</t>
+          <t>Music Tutoring</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -20141,27 +20141,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -20170,52 +20170,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>53ef6b05-244d-4400-bb30-39df9747dc8f</t>
+          <t>0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Music Tutoring</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tutoring</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Valerie</t>
+          <t>April Amante</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -20224,32 +20224,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>10c007c2-c79f-4fd8-a74e-9728b99ffba3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>April Amante</t>
+          <t>Charlotte Wilkins</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20259,12 +20259,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -20278,7 +20278,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10c007c2-c79f-4fd8-a74e-9728b99ffba3</t>
+          <t>23fecadf-0679-4e79-b8f4-f9643ddde586</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Cameron Wilkins</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -20318,12 +20318,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -20332,32 +20332,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>23fecadf-0679-4e79-b8f4-f9643ddde586</t>
+          <t>5d0d245e-af1e-46cc-bd7a-c220cf7938f1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Office Hours</t>
+          <t>AMP Transfer Workshop</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cameron Wilkins</t>
+          <t>Charlotte Wilkins</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20367,17 +20367,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -20386,12 +20386,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5d0d245e-af1e-46cc-bd7a-c220cf7938f1</t>
+          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMP Transfer Workshop</t>
+          <t>AMP Week 4 Meeting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -20426,12 +20426,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>14:15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -20440,12 +20440,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>af96aab8-9ed1-4616-90e5-3b1028b23842</t>
+          <t>0f43e932-7e74-4c7e-bcc2-e4e49e550f24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMP Week 4 Meeting</t>
+          <t>AMP Transfer Workshop</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -20470,22 +20470,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -20494,52 +20494,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0f43e932-7e74-4c7e-bcc2-e4e49e550f24</t>
+          <t>0ff1d3c5-313b-4afa-b46e-282bfc532844</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMP Transfer Workshop</t>
+          <t>Tutoring</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>tutoring</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Valerie</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -20548,27 +20548,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0ff1d3c5-313b-4afa-b46e-282bfc532844</t>
+          <t>97131d93-2a09-4ad6-a366-f22a3a1f9440</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tutoring</t>
+          <t>Intro to Recording</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tutoring</t>
+          <t>class</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Valerie</t>
+          <t>Mark Cross</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -20588,12 +20588,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -20602,52 +20602,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>97131d93-2a09-4ad6-a366-f22a3a1f9440</t>
+          <t>8da3234c-c8ba-4f68-8a9b-66ea350409cc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Intro to Recording</t>
+          <t>Student Accommodation - Datis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mark Cross</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday; Wednesday</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -20656,52 +20656,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8da3234c-c8ba-4f68-8a9b-66ea350409cc</t>
+          <t>bfe10a39-daf6-42c3-ba1b-6700bdf68071</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Student Accommodation - Datis</t>
+          <t>College Choir Sectionals</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>class</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Barmey</t>
+          <t>Gaga</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monday; Wednesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -20710,32 +20710,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bfe10a39-daf6-42c3-ba1b-6700bdf68071</t>
+          <t>e6a31aa2-7894-4852-87bd-5b57dd0ea489</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>College Choir Sectionals</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Gaga</t>
+          <t>Mark Cross</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3414-M (Commercial)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday; Tuesday; Wednesday; Thursday</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -20745,17 +20745,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -20764,52 +20764,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>e6a31aa2-7894-4852-87bd-5b57dd0ea489</t>
+          <t>2a209309-7250-48f0-8971-2439d1202b66</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Office Hours</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mark Cross</t>
+          <t>Sophia Reyes</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3414-M (Commercial)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monday; Tuesday; Wednesday; Thursday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -20818,27 +20818,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2a209309-7250-48f0-8971-2439d1202b66</t>
+          <t>77a65a10-a59a-4f96-a76b-94077f9e3578</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rehearsal</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sophia Reyes</t>
+          <t>Holly Palmer</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -20858,12 +20858,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -20872,52 +20872,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>77a65a10-a59a-4f96-a76b-94077f9e3578</t>
+          <t>222a7106-bf8f-4e4c-8d02-b585a311396c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Holly Palmer</t>
+          <t>Simone, Khalel, Jace, Gabriel Ortiz, Gabriel Magana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3414-J (Lance)</t>
+          <t>3414-K (Perc)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -20926,7 +20926,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>222a7106-bf8f-4e4c-8d02-b585a311396c</t>
+          <t>c242808b-916e-4faf-8cb3-31874d7f3fb2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -20941,17 +20941,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Simone, Khalel, Jace, Gabriel Ortiz, Gabriel Magana</t>
+          <t>Nicole Shaynis</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3414-K (Perc)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -20974,96 +20974,96 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Gabe O Gabriel M Shimone Sophia Reyes Valerie Siegler Hamta Jesse James  Nicole Sheynis</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>c242808b-916e-4faf-8cb3-31874d7f3fb2</t>
+          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rehearsal</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rehearsal</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nicole Shaynis</t>
+          <t>Wendy Mazon</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Gabe O Gabriel M Shimone Sophia Reyes Valerie Siegler Hamta Jesse James  Nicole Sheynis</t>
-        </is>
-      </c>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
+          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Office Hours</t>
+          <t>Music Tutoring</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wendy Mazon</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -21073,17 +21073,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -27357,7 +27357,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:08 UTC</t>
+          <t>2026-10-14 15:44 UTC</t>
         </is>
       </c>
     </row>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21038,32 +21038,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
+          <t>51aa789c-5701-46de-83dd-5154b51b00dd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Music Tutoring</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Wendy Mazon</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -21073,17 +21073,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -21092,32 +21092,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>51aa789c-5701-46de-83dd-5154b51b00dd</t>
+          <t>bd5affa3-07c7-41bc-847f-7af2e06f794b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Office Hours</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wendy Mazon</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -21127,20 +21127,24 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Jocelyn, Jose, Yury, Ian, Angelo</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -21200,27 +21204,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>Music Tutoring</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -21230,22 +21234,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -21254,12 +21258,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -21274,7 +21278,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -21284,17 +21288,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -21302,22 +21306,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -21342,12 +21342,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -21370,17 +21370,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21390,7 +21390,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -21400,17 +21400,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -21418,23 +21418,27 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -21444,7 +21448,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -21454,12 +21458,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -21478,60 +21482,114 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27357,7 +27415,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 15:44 UTC</t>
+          <t>2026-10-15 15:31 UTC</t>
         </is>
       </c>
     </row>
@@ -27380,7 +27438,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21258,52 +21258,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>5e58f09a-9063-45c8-912c-2cdc681c58d5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Doug Mattingly</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -21312,12 +21312,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -21342,17 +21342,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -21360,22 +21360,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -21400,12 +21396,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -21420,7 +21416,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -21428,17 +21424,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -21448,7 +21444,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -21458,17 +21454,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -21476,23 +21472,27 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -21502,7 +21502,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -21512,12 +21512,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -21536,60 +21536,114 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23499,25 +23553,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -23939,25 +23985,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -24463,25 +24501,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -24987,25 +25017,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -25427,25 +25449,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -25867,25 +25881,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -26307,25 +26313,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -26747,25 +26745,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -27161,25 +27151,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -27415,7 +27397,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:31 UTC</t>
+          <t>2026-10-19 17:22 UTC</t>
         </is>
       </c>
     </row>
@@ -27438,7 +27420,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21312,27 +21312,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>6a667951-c0c6-4100-b5b9-5745a07eceef</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -21342,36 +21342,40 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>James, Mark Gallardo, Joshua</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -21386,7 +21390,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -21396,17 +21400,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -21414,22 +21418,18 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -21454,12 +21454,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -21482,17 +21482,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -21502,7 +21502,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -21512,17 +21512,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -21530,23 +21530,27 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -21556,7 +21560,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -21566,12 +21570,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -21590,60 +21594,114 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21656,7 +21714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23406,12 +23464,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
+          <t>res:6a667951-c0c6-4100-b5b9-5745a07eceef__2026-10-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:6a667951-c0c6-4100-b5b9-5745a07eceef</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -23421,27 +23479,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3414-J (Lance)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(pending)</t>
+          <t>James, Mark Gallardo, Joshua</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-20</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -23451,66 +23521,70 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
+          <t>tue-3414-a-practice-0945__2026-10-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-21</t>
+          <t>tue-3414-k-perc-1615__2026-10-20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-k-perc-1615</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -23520,17 +23594,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-K (Perc)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>14:15</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -23538,12 +23612,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -23559,21 +23633,17 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-10-21</t>
+          <t>wed-3400-choir-1415__2026-10-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -23588,17 +23658,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -23606,17 +23676,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
+          <t>wed-3414-k-perc-1300__2026-10-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -23627,22 +23697,26 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-22</t>
+          <t>wed-3424-piano-lab-1015__2026-10-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -23652,17 +23726,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -23670,12 +23744,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-10-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -23685,82 +23759,94 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
+          <t>thu-3414-k-perc-0945__2026-10-22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
+          <t>thu-3423-1315__2026-10-22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -23770,7 +23856,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -23786,7 +23872,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -23796,7 +23882,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -23812,7 +23898,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -23822,7 +23908,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -23838,42 +23924,38 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-10-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -23883,66 +23965,58 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-10-27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>tue-3414-a-practice-0945__2026-10-27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -23952,17 +24026,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -23970,12 +24044,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -23991,21 +24065,17 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-10-28</t>
+          <t>wed-3400-choir-1415__2026-10-28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -24020,17 +24090,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -24038,17 +24108,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
+          <t>wed-3414-k-perc-1300__2026-10-28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -24059,22 +24129,26 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>wed-3424-piano-lab-1015__2026-10-28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -24084,34 +24158,30 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -24121,39 +24191,23 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>3414-B (Practice)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-29</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -24168,12 +24222,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -24181,17 +24235,21 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-10-29</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -24206,77 +24264,105 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
+          <t>thu-3423-1315__2026-10-29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -24286,7 +24372,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -24302,7 +24388,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -24312,7 +24398,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -24328,7 +24414,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -24338,7 +24424,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -24354,42 +24440,38 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -24399,66 +24481,58 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -24468,17 +24542,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -24486,12 +24560,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -24507,21 +24581,17 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-04</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -24536,17 +24606,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -24554,17 +24624,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -24575,22 +24645,26 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>wed-3424-piano-lab-1015__2026-11-04</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -24600,34 +24674,30 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -24637,39 +24707,23 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>3414-B (Practice)</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-05</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -24684,12 +24738,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -24697,17 +24751,21 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-05</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -24722,77 +24780,105 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
+          <t>thu-3423-1315__2026-11-05</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -24802,7 +24888,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -24818,7 +24904,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -24828,7 +24914,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -24844,7 +24930,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -24854,7 +24940,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -24870,42 +24956,38 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -24915,66 +24997,58 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -24984,17 +25058,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -25002,12 +25076,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -25023,21 +25097,17 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-11</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -25052,17 +25122,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -25070,17 +25140,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -25091,22 +25161,26 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>wed-3424-piano-lab-1015__2026-11-11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -25116,17 +25190,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -25134,12 +25208,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -25149,82 +25223,94 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
+          <t>thu-3423-1315__2026-11-12</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -25234,7 +25320,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -25250,7 +25336,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -25260,7 +25346,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -25276,7 +25362,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -25286,7 +25372,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -25302,42 +25388,38 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -25347,66 +25429,58 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -25416,17 +25490,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -25434,12 +25508,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -25455,21 +25529,17 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-18</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -25484,17 +25554,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -25502,17 +25572,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -25523,22 +25593,26 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>wed-3424-piano-lab-1015__2026-11-18</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -25548,17 +25622,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -25566,12 +25640,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -25581,82 +25655,94 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
+          <t>thu-3423-1315__2026-11-19</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -25666,7 +25752,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25682,7 +25768,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -25692,7 +25778,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25708,7 +25794,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -25718,7 +25804,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25734,42 +25820,38 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -25779,66 +25861,58 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -25848,17 +25922,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -25866,12 +25940,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -25887,21 +25961,17 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-25</t>
+          <t>wed-3400-choir-1415__2026-11-25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -25916,17 +25986,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -25934,17 +26004,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -25955,22 +26025,26 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>wed-3424-piano-lab-1015__2026-11-25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -25980,17 +26054,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -25998,12 +26072,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -26013,82 +26087,94 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+          <t>thu-3423-1315__2026-11-26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -26098,7 +26184,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -26114,7 +26200,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -26124,7 +26210,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -26140,7 +26226,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -26150,7 +26236,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -26166,42 +26252,38 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -26211,66 +26293,58 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -26280,17 +26354,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -26298,12 +26372,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -26319,21 +26393,17 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-02</t>
+          <t>wed-3400-choir-1415__2026-12-02</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -26348,17 +26418,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -26366,17 +26436,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -26387,22 +26457,26 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>wed-3424-piano-lab-1015__2026-12-02</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -26412,17 +26486,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -26430,12 +26504,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -26445,82 +26519,94 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+          <t>thu-3423-1315__2026-12-03</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -26530,7 +26616,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -26546,7 +26632,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -26556,7 +26642,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -26572,7 +26658,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -26582,7 +26668,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -26598,42 +26684,38 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -26643,66 +26725,58 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26712,17 +26786,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -26730,12 +26804,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -26751,21 +26825,17 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-09</t>
+          <t>wed-3400-choir-1415__2026-12-09</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -26780,17 +26850,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
@@ -26798,17 +26868,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -26819,22 +26889,26 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>wed-3424-piano-lab-1015__2026-12-09</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -26844,17 +26918,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -26862,12 +26936,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -26877,82 +26951,94 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+          <t>thu-3423-1315__2026-12-10</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -26962,7 +27048,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -26978,7 +27064,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -26988,7 +27074,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27004,7 +27090,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -27014,7 +27100,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -27030,42 +27116,38 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -27075,103 +27157,91 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-16</t>
+          <t>wed-3400-choir-1415__2026-12-16</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -27186,17 +27256,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -27204,78 +27274,146 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-17</t>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
+          <t>wed-3424-piano-lab-1015__2026-12-16</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>wed-3424-piano-lab-1015</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945__2026-12-17</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
           <t>thu-3423-1315__2026-12-17</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>thu-3423-1315</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>3422</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27397,7 +27535,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:22 UTC</t>
+          <t>2026-10-21 15:52 UTC</t>
         </is>
       </c>
     </row>
@@ -27420,7 +27558,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -27430,7 +27568,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20984,61 +20984,65 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
+          <t>ce180352-78c5-4852-9c2a-ace20689961c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Office Hours</t>
+          <t>PW Rehearsal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wendy Mazon</t>
+          <t>Nicole Shamas</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3414-L (Michelle)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Jesse (Cello), Sophia, Asia, 2 gabriels</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>51aa789c-5701-46de-83dd-5154b51b00dd</t>
+          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21078,12 +21082,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -21092,32 +21096,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bd5affa3-07c7-41bc-847f-7af2e06f794b</t>
+          <t>51aa789c-5701-46de-83dd-5154b51b00dd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rehearsal</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rehearsal</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Wendy Mazon</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -21127,50 +21131,46 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Jocelyn, Jose, Yury, Ian, Angelo</t>
-        </is>
-      </c>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>bd5affa3-07c7-41bc-847f-7af2e06f794b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -21180,36 +21180,40 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Jocelyn, Jose, Yury, Ian, Angelo</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Music Tutoring</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -21219,12 +21223,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Charlotte Wilkins</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -21244,12 +21248,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -21258,52 +21262,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5e58f09a-9063-45c8-912c-2cdc681c58d5</t>
+          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>Music Tutoring</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Doug Mattingly</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -21312,85 +21316,81 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6a667951-c0c6-4100-b5b9-5745a07eceef</t>
+          <t>5e58f09a-9063-45c8-912c-2cdc681c58d5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rehearsal</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Barmey</t>
+          <t>Doug Mattingly</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3414-J (Lance)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>James, Mark Gallardo, Joshua</t>
-        </is>
-      </c>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>6a667951-c0c6-4100-b5b9-5745a07eceef</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -21400,51 +21400,55 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>James, Mark Gallardo, Joshua</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>816db2e7-7490-4046-879b-5f6fa45228dd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Justine Boonstra</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -21454,40 +21458,36 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -21502,7 +21502,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -21512,17 +21512,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -21530,37 +21530,33 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>d4afe0e9-5876-407b-ab65-09597337ca9c</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Carson Schafer</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3414-K (Perc)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -21570,22 +21566,22 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -21594,27 +21590,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>d91f2720-1a84-4291-8fb9-27c530cd0c88</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Justine Boonstra</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -21624,22 +21620,22 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -21648,60 +21644,284 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AMP Composition Presentation Run-thru</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AMP Composition Presentation</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27535,7 +27755,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 15:52 UTC</t>
+          <t>2026-10-23 15:40 UTC</t>
         </is>
       </c>
     </row>
@@ -27558,7 +27778,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21042,61 +21042,65 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
+          <t>944a9fc6-72b3-49a6-a4a7-ce52286d30a2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Office Hours</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wendy Mazon</t>
+          <t>Marco Ibrahim</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3414-L (Michelle)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Shimone, Gabrielle, Gabrielle, Marco</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>51aa789c-5701-46de-83dd-5154b51b00dd</t>
+          <t>1a597498-d884-4d89-a1dd-596453f537c4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -21136,12 +21140,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -21150,32 +21154,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bd5affa3-07c7-41bc-847f-7af2e06f794b</t>
+          <t>51aa789c-5701-46de-83dd-5154b51b00dd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rehearsal</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rehearsal</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Wendy Mazon</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -21185,50 +21189,46 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Jocelyn, Jose, Yury, Ian, Angelo</t>
-        </is>
-      </c>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
+          <t>bd5affa3-07c7-41bc-847f-7af2e06f794b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>Rehearsal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -21238,36 +21238,40 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Jocelyn, Jose, Yury, Ian, Angelo</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
+          <t>0084d402-4dbb-427c-bcf6-d813dbb094aa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Music Tutoring</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -21277,12 +21281,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Charlotte Wilkins</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -21302,12 +21306,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -21316,52 +21320,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5e58f09a-9063-45c8-912c-2cdc681c58d5</t>
+          <t>4196668a-ca5b-42ae-9714-3f20da4d1220</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>Music Tutoring</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Doug Mattingly</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>every day</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -21370,85 +21374,81 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6a667951-c0c6-4100-b5b9-5745a07eceef</t>
+          <t>5e58f09a-9063-45c8-912c-2cdc681c58d5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>rehearsal</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Barmey</t>
+          <t>Doug Mattingly</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3414-J (Lance)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>James, Mark Gallardo, Joshua</t>
-        </is>
-      </c>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>816db2e7-7490-4046-879b-5f6fa45228dd</t>
+          <t>6a667951-c0c6-4100-b5b9-5745a07eceef</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Justine Boonstra</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -21458,51 +21458,55 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>James, Mark Gallardo, Joshua</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
+          <t>816db2e7-7490-4046-879b-5f6fa45228dd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AMP Week 8 Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Justine Boonstra</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -21522,12 +21526,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -21536,27 +21540,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>d4afe0e9-5876-407b-ab65-09597337ca9c</t>
+          <t>a3cd0091-1a15-4104-b635-ab3ea5123476</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>AMP Week 8 Meeting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Carson Schafer</t>
+          <t>Charlotte Wilkins</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3414-K (Perc)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -21576,12 +21580,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -21590,7 +21594,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>d91f2720-1a84-4291-8fb9-27c530cd0c88</t>
+          <t>d4afe0e9-5876-407b-ab65-09597337ca9c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -21605,12 +21609,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Justine Boonstra</t>
+          <t>Carson Schafer</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3414-J (Lance)</t>
+          <t>3414-K (Perc)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -21630,12 +21634,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -21644,27 +21648,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>d91f2720-1a84-4291-8fb9-27c530cd0c88</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Justine Boonstra</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -21674,40 +21678,36 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -21732,12 +21732,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -21760,17 +21760,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -21790,17 +21790,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -21808,23 +21808,27 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -21834,7 +21838,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -21844,12 +21848,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -21868,60 +21872,114 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27755,7 +27813,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:40 UTC</t>
+          <t>2026-10-24 14:20 UTC</t>
         </is>
       </c>
     </row>
@@ -27778,7 +27836,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19881,7 +19881,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -21702,27 +21702,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>c82ca63b-0fb3-49d7-8454-a58bcb38bb52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>April Amante</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -21732,45 +21732,41 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>feb2327b-6d6c-46f1-8e2f-1e020aa8f116</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>Office Hours</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -21780,65 +21776,61 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>98cdaddb-d419-44ed-9388-fe7b822dddb7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>April Amante</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -21848,22 +21840,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -21872,27 +21864,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>590bfb5e-2ba1-44d8-a856-401f8ef5dfb9</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Justine Boonstra</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -21902,22 +21894,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -21926,60 +21918,446 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>85a0f47f-18bd-4f41-aaa2-f7e93b13fa83</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AMP Lessons</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>amp</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Justine Boonstra</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3414-C (Practice)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AMP Composition Presentation Run-thru</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>df8f388d-d463-4309-9142-98f2c85cb58f</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AMP Lessons</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>amp</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>April Amante</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3414-J (Lance)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>e0c0344a-4136-48de-851e-d3b304f34f50</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AMP Lessons</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>amp</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bradley Moller</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AMP Composition Presentation</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21992,7 +22370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24309,7 +24687,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -24348,12 +24726,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-10-28</t>
+          <t>wed-3414-k-perc-1300__2026-10-28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -24363,35 +24741,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-10-28</t>
+          <t>wed-3424-piano-lab-1015__2026-10-28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -24401,65 +24771,61 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-10-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-29</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -24469,23 +24835,39 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -24500,12 +24882,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -24515,19 +24897,19 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -24542,12 +24924,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -24555,21 +24937,17 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-29</t>
+          <t>thu-3423-1315__2026-10-29</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -24584,17 +24962,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -24602,45 +24980,33 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-10-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -24650,7 +25016,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -24666,7 +25032,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -24676,7 +25042,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -24692,7 +25058,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -24702,7 +25068,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -24718,7 +25084,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -24728,7 +25094,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -24744,12 +25110,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -24759,23 +25125,27 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -24785,65 +25155,61 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -24853,23 +25219,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -24879,35 +25257,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-04</t>
+          <t>wed-3424-piano-lab-1015__2026-11-04</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -24917,65 +25287,61 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -24985,23 +25351,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>3401 (Band)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -25016,12 +25398,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -25031,19 +25413,19 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -25058,12 +25440,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -25071,21 +25453,17 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-05</t>
+          <t>thu-3423-1315__2026-11-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -25100,17 +25478,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -25118,45 +25496,33 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -25166,7 +25532,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -25182,7 +25548,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -25192,7 +25558,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -25208,7 +25574,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -25218,7 +25584,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -25234,7 +25600,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -25244,7 +25610,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -25260,12 +25626,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -25275,23 +25641,27 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -25301,65 +25671,61 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -25369,23 +25735,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -25395,35 +25773,27 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>wed-3424-piano-lab-1015__2026-11-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -25433,65 +25803,61 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -25501,23 +25867,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>thu-3423-1315__2026-11-12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -25532,17 +25910,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -25550,45 +25928,33 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -25598,7 +25964,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -25614,7 +25980,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -25624,7 +25990,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -25640,7 +26006,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -25650,7 +26016,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -25666,7 +26032,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -25676,7 +26042,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -25692,12 +26058,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -25707,23 +26073,27 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -25733,65 +26103,61 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -25801,23 +26167,35 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -25827,35 +26205,27 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>wed-3424-piano-lab-1015__2026-11-18</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -25865,65 +26235,61 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -25933,23 +26299,35 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>thu-3423-1315__2026-11-19</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -25964,17 +26342,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -25982,45 +26360,33 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -26030,7 +26396,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -26046,7 +26412,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -26056,7 +26422,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -26072,7 +26438,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -26082,7 +26448,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -26098,7 +26464,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -26108,7 +26474,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -26124,12 +26490,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -26139,23 +26505,27 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -26165,65 +26535,61 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+          <t>wed-3400-choir-1415__2026-11-25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -26233,23 +26599,35 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -26259,35 +26637,27 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>wed-3424-piano-lab-1015__2026-11-25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -26297,65 +26667,61 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -26365,23 +26731,35 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>thu-3423-1315__2026-11-26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -26396,17 +26774,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -26414,45 +26792,33 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -26462,7 +26828,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -26478,7 +26844,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -26488,7 +26854,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -26504,7 +26870,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -26514,7 +26880,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -26530,7 +26896,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -26540,7 +26906,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -26556,12 +26922,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -26571,23 +26937,27 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -26597,65 +26967,61 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+          <t>wed-3400-choir-1415__2026-12-02</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -26665,23 +27031,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -26691,35 +27069,27 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>wed-3424-piano-lab-1015__2026-12-02</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -26729,65 +27099,61 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -26797,23 +27163,35 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>thu-3423-1315__2026-12-03</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -26828,17 +27206,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -26846,45 +27224,33 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -26894,7 +27260,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -26910,7 +27276,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -26920,7 +27286,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -26936,7 +27302,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -26946,7 +27312,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -26962,7 +27328,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -26972,7 +27338,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26988,12 +27354,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -27003,23 +27369,27 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -27029,65 +27399,61 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+          <t>wed-3400-choir-1415__2026-12-09</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -27097,23 +27463,35 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -27123,35 +27501,27 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>wed-3424-piano-lab-1015__2026-12-09</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -27161,65 +27531,61 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -27229,23 +27595,35 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>thu-3423-1315__2026-12-10</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -27260,17 +27638,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -27278,45 +27656,33 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -27326,7 +27692,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27342,7 +27708,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -27352,7 +27718,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27368,7 +27734,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -27378,7 +27744,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -27394,7 +27760,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -27404,7 +27770,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -27420,12 +27786,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -27435,23 +27801,27 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>noted</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -27461,32 +27831,40 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>noted</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>wed-3400-choir-1415__2026-12-16</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -27496,17 +27874,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>3414-A (Practice)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -27514,12 +27892,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -27529,35 +27907,27 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>wed-3424-piano-lab-1015__2026-12-16</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -27567,32 +27937,40 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-16</t>
+          <t>thu-3414-k-perc-0945__2026-12-17</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -27602,17 +27980,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>3424 (Piano lab)</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
@@ -27620,12 +27998,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-17</t>
+          <t>thu-3423-1315__2026-12-17</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -27640,58 +28018,20 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>thu-3423-1315__2026-12-17</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>thu-3423-1315</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27813,7 +28153,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24 14:20 UTC</t>
+          <t>2026-10-27 16:16 UTC</t>
         </is>
       </c>
     </row>
@@ -27836,7 +28176,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -27846,7 +28186,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21864,22 +21864,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>590bfb5e-2ba1-44d8-a856-401f8ef5dfb9</t>
+          <t>2df91151-0c7e-475c-ac1d-27caac361178</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Justine Boonstra</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -21904,21 +21904,25 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Sophia, Jackson Wilson, Ethan Dorcey, Joshua Valle, James Elle, Valerie Sigler, Shimone,</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>85a0f47f-18bd-4f41-aaa2-f7e93b13fa83</t>
+          <t>590bfb5e-2ba1-44d8-a856-401f8ef5dfb9</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -21938,7 +21942,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3414-C (Practice)</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -21958,12 +21962,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -21972,27 +21976,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>85a0f47f-18bd-4f41-aaa2-f7e93b13fa83</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Justine Boonstra</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-C (Practice)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -22012,45 +22016,41 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>df8f388d-d463-4309-9142-98f2c85cb58f</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>April Amante</t>
+          <t>Charlotte Wilkins</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3414-J (Lance)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -22060,51 +22060,55 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>e0c0344a-4136-48de-851e-d3b304f34f50</t>
+          <t>f088e352-405c-414f-8919-be12cc1d62f8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>Marco Ibrahim</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bradley Moller</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3414-L (Michelle)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -22114,51 +22118,55 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Shimone, Gabriel, Gabe</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>3a3d1ae4-bb68-49c4-8956-f94b21de8247</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>Marco Ibrahim</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-L (Michelle)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -22168,27 +22176,27 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+          <t>Shimone, Gabriel, Gabe</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -22196,27 +22204,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>df8f388d-d463-4309-9142-98f2c85cb58f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>April Amante</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -22226,22 +22234,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -22250,27 +22258,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>e0c0344a-4136-48de-851e-d3b304f34f50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Bradley Moller</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -22280,22 +22288,22 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -22304,60 +22312,226 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AMP Composition Presentation</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AMP Leadership Meeting</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>checkout</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3416-B (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28153,7 +28327,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 16:16 UTC</t>
+          <t>2026-10-29 17:20 UTC</t>
         </is>
       </c>
     </row>
@@ -28176,7 +28350,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -19764,7 +19764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21922,32 +21922,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>590bfb5e-2ba1-44d8-a856-401f8ef5dfb9</t>
+          <t>3bd5b720-de9a-477a-9f01-61e5eaeeb309</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>NO Band Rehearsals</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>amp</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Justine Boonstra</t>
-        </is>
-      </c>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3414-J (Lance)</t>
+          <t>3414-L (Michelle)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -21957,26 +21953,30 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No Group Rehearsals next to Commercial Music during this time</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>85a0f47f-18bd-4f41-aaa2-f7e93b13fa83</t>
+          <t>590bfb5e-2ba1-44d8-a856-401f8ef5dfb9</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3414-C (Practice)</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -22016,12 +22016,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -22030,12 +22030,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
+          <t>80227d67-91da-4e2b-a833-8a65bffb8837</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation Run-thru</t>
+          <t>Music Club</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -22045,17 +22045,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>every day</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -22065,50 +22065,46 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>f088e352-405c-414f-8919-be12cc1d62f8</t>
+          <t>85a0f47f-18bd-4f41-aaa2-f7e93b13fa83</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marco Ibrahim</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rehearsal</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Barmey</t>
+          <t>Justine Boonstra</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3414-L (Michelle)</t>
+          <t>3414-C (Practice)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -22128,45 +22124,41 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Shimone, Gabriel, Gabe</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3a3d1ae4-bb68-49c4-8956-f94b21de8247</t>
+          <t>a397bbca-e4df-4f5a-9bcc-c7525d8c7235</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marco Ibrahim</t>
+          <t>AMP Composition Presentation Run-thru</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rehearsal</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Barmey</t>
+          <t>Charlotte Wilkins</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3414-L (Michelle)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -22176,27 +22168,27 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Shimone, Gabriel, Gabe</t>
+          <t>Moved MUS 165 for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -22204,27 +22196,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>df8f388d-d463-4309-9142-98f2c85cb58f</t>
+          <t>3a3d1ae4-bb68-49c4-8956-f94b21de8247</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AMP Lessons</t>
+          <t>Marco Ibrahim</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>amp</t>
+          <t>rehearsal</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>April Amante</t>
+          <t>Barmey</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3414-J (Lance)</t>
+          <t>3414-L (Michelle)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -22244,21 +22236,25 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Shimone, Gabriel, Gabe</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>e0c0344a-4136-48de-851e-d3b304f34f50</t>
+          <t>df8f388d-d463-4309-9142-98f2c85cb58f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -22273,12 +22269,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bradley Moller</t>
+          <t>April Amante</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3414-J (Lance)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -22298,12 +22294,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -22312,27 +22308,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
+          <t>e0c0344a-4136-48de-851e-d3b304f34f50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AMP Composition Presentation</t>
+          <t>AMP Lessons</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>amp</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Charlotte Wilkins</t>
+          <t>Bradley Moller</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -22342,45 +22338,41 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
+          <t>715ceac4-1e20-4ad0-a8e9-d05004d454a3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMP Leadership Meeting</t>
+          <t>AMP Composition Presentation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -22390,7 +22382,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3416-B (Adjunct Office)</t>
+          <t>3400 (Choir)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -22400,17 +22392,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -22418,23 +22410,27 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Moved MUS 165 for AMP Comp. Presentation; confirmed w/Mark</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+          <t>fb0d5166-4821-4ab1-b074-b10761481d37</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMP Week 12 Meeting</t>
+          <t>AMP Leadership Meeting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -22444,7 +22440,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-B (Adjunct Office)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -22454,12 +22450,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -22478,60 +22474,114 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>4ff8123a-9402-4d74-9954-936a5cc216b1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AMP Week 12 Meeting</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Charlotte Wilkins</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>every day</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>e12045dd-fb26-491a-a133-f3976c637d47</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Dance Conference</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>event</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Wendy</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>3400 (Choir); 3401 (Band)</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>every day</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>2027-02-03</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>2027-02-06</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>00:00</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>23:59</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>They will have their own volunteers monitor the rooms</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22544,7 +22594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24994,12 +25044,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-10-29</t>
+          <t>res:3bd5b720-de9a-477a-9f01-61e5eaeeb309__2026-10-29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:3bd5b720-de9a-477a-9f01-61e5eaeeb309</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -25014,34 +25064,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>3401 (Band)</t>
+          <t>3414-L (Michelle)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
+          <t>No Group Rehearsals next to Commercial Music during this time</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-10-29</t>
+          <t>thu-3400-choir-1110__2026-10-29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -25056,12 +25106,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -25071,19 +25121,19 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+          <t>Moved for AMP Comp. Presentation Run-thru; confirmed w/Mark</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-10-29</t>
+          <t>thu-3401-band-1145__2026-10-29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -25098,12 +25148,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -25111,17 +25161,21 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-10-29</t>
+          <t>thu-3414-k-perc-0945__2026-10-29</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -25136,17 +25190,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -25154,33 +25208,45 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
+          <t>thu-3423-1315__2026-10-29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -25190,7 +25256,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -25206,7 +25272,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-10-31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -25216,7 +25282,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -25232,7 +25298,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -25242,7 +25308,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -25258,7 +25324,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -25268,7 +25334,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -25284,12 +25350,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -25299,27 +25365,23 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-03</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -25329,61 +25391,65 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
+          <t>tue-3414-a-practice-0945__2026-11-03</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-04</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -25393,35 +25459,23 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-04</t>
+          <t>wed-3400-choir-1415__2026-11-04</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -25431,27 +25485,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-04</t>
+          <t>wed-3414-k-perc-1300__2026-11-04</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -25461,61 +25523,65 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
+          <t>wed-3424-piano-lab-1015__2026-11-04</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110__2026-11-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>thu-3400-choir-1110</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -25525,39 +25591,23 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>3401 (Band)</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145__2026-11-05</t>
+          <t>thu-3400-choir-1110__2026-11-05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>thu-3401-band-1145</t>
+          <t>thu-3400-choir-1110</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -25572,12 +25622,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3414-B (Practice)</t>
+          <t>3401 (Band)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -25587,19 +25637,19 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+          <t>Moved for AMP Comp. Presentation; confirmed w/Mark</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-05</t>
+          <t>thu-3401-band-1145__2026-11-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>thu-3401-band-1145</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -25614,12 +25664,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3414-B (Practice)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -25627,17 +25677,21 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Moved for AMP Comp. Presentation which pushes MUS 165</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-05</t>
+          <t>thu-3414-k-perc-0945__2026-11-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -25652,17 +25706,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -25670,33 +25724,45 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
+          <t>thu-3423-1315__2026-11-05</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-06</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -25706,7 +25772,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -25722,7 +25788,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-07</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -25732,7 +25798,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -25748,7 +25814,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-08</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -25758,7 +25824,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -25774,7 +25840,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-09</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -25784,7 +25850,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -25800,12 +25866,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -25815,27 +25881,23 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-10</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -25845,61 +25907,65 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
+          <t>tue-3414-a-practice-0945__2026-11-10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-11</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -25909,35 +25975,23 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-11</t>
+          <t>wed-3400-choir-1415__2026-11-11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -25947,27 +26001,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-11</t>
+          <t>wed-3414-k-perc-1300__2026-11-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -25977,61 +26039,65 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
+          <t>wed-3424-piano-lab-1015__2026-11-11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -26041,35 +26107,23 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-12</t>
+          <t>thu-3414-k-perc-0945__2026-11-12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -26084,17 +26138,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -26102,33 +26156,45 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
+          <t>thu-3423-1315__2026-11-12</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-13</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -26138,7 +26204,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -26154,7 +26220,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-14</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -26164,7 +26230,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -26180,7 +26246,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-15</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -26190,7 +26256,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -26206,7 +26272,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-16</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -26216,7 +26282,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -26232,12 +26298,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-17</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -26247,27 +26313,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-17</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-17</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -26277,61 +26339,65 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
+          <t>tue-3414-a-practice-0945__2026-11-17</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-18</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-18</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -26341,35 +26407,23 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-18</t>
+          <t>wed-3400-choir-1415__2026-11-18</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -26379,27 +26433,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-18</t>
+          <t>wed-3414-k-perc-1300__2026-11-18</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -26409,61 +26471,65 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
+          <t>wed-3424-piano-lab-1015__2026-11-18</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-19</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-19</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -26473,35 +26539,23 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-19</t>
+          <t>thu-3414-k-perc-0945__2026-11-19</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -26516,17 +26570,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -26534,33 +26588,45 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
+          <t>thu-3423-1315__2026-11-19</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-20</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -26570,7 +26636,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -26586,7 +26652,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-21</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -26596,7 +26662,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -26612,7 +26678,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-22</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -26622,7 +26688,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -26638,7 +26704,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-23</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -26648,7 +26714,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -26664,12 +26730,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-24</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -26679,27 +26745,23 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-11-24</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-11-24</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -26709,61 +26771,65 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
+          <t>tue-3414-a-practice-0945__2026-11-24</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-11-25</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -26773,35 +26839,23 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-11-25</t>
+          <t>wed-3400-choir-1415__2026-11-25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -26811,27 +26865,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-11-25</t>
+          <t>wed-3414-k-perc-1300__2026-11-25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -26841,61 +26903,65 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
+          <t>wed-3424-piano-lab-1015__2026-11-25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-11-26</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -26905,35 +26971,23 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-11-26</t>
+          <t>thu-3414-k-perc-0945__2026-11-26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -26948,17 +27002,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -26966,33 +27020,45 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
+          <t>thu-3423-1315__2026-11-26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-27</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -27002,7 +27068,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -27018,7 +27084,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-28</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -27028,7 +27094,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -27044,7 +27110,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-29</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -27054,7 +27120,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -27070,7 +27136,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-11-30</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -27080,7 +27146,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -27096,12 +27162,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-01</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -27111,27 +27177,23 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-01</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-01</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -27141,61 +27203,65 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
+          <t>tue-3414-a-practice-0945__2026-12-01</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-02</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-02</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -27205,35 +27271,23 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-02</t>
+          <t>wed-3400-choir-1415__2026-12-02</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -27243,27 +27297,35 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-02</t>
+          <t>wed-3414-k-perc-1300__2026-12-02</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -27273,61 +27335,65 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
+          <t>wed-3424-piano-lab-1015__2026-12-02</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-03</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -27337,35 +27403,23 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-12-03</t>
+          <t>thu-3414-k-perc-0945__2026-12-03</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -27380,17 +27434,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -27398,33 +27452,45 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
+          <t>thu-3423-1315__2026-12-03</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-04</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -27434,7 +27500,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -27450,7 +27516,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-05</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -27460,7 +27526,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -27476,7 +27542,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-06</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -27486,7 +27552,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -27502,7 +27568,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-07</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -27512,7 +27578,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -27528,12 +27594,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-08</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -27543,27 +27609,23 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-08</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-08</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -27573,61 +27635,65 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
+          <t>tue-3414-a-practice-0945__2026-12-08</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>3414-A (Practice)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-09</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-09</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -27637,35 +27703,23 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>3400 (Choir)</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-09</t>
+          <t>wed-3400-choir-1415__2026-12-09</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -27675,27 +27729,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-09</t>
+          <t>wed-3414-k-perc-1300__2026-12-09</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -27705,61 +27767,65 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
+          <t>wed-3424-piano-lab-1015__2026-12-09</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>3424 (Piano lab)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-10</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-10</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -27769,35 +27835,23 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>3416-D (Adjunct Office)</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>thu-3423-1315__2026-12-10</t>
+          <t>thu-3414-k-perc-0945__2026-12-10</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>thu-3423-1315</t>
+          <t>thu-3414-k-perc-0945</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -27812,17 +27866,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3416-D (Adjunct Office)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
           <t>13:15</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>19:15</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -27830,33 +27884,45 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
+          <t>thu-3423-1315__2026-12-10</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
+          <t>thu-3423-1315</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-11</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -27866,7 +27932,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27882,7 +27948,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-12</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -27892,7 +27958,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27908,7 +27974,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-13</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -27918,7 +27984,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -27934,7 +28000,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-14</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -27944,7 +28010,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -27960,12 +28026,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3__2026-12-15</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
+          <t>res:0cf55fb2-6df7-4650-9729-59d7edb758c3</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -27975,27 +28041,23 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>noted</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>(pending)</t>
-        </is>
-      </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945__2026-12-15</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0__2026-12-15</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>tue-3414-a-practice-0945</t>
+          <t>res:d95c8dbd-5e86-4f75-8311-8411d2f9b2c0</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -28005,40 +28067,32 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>3414-A (Practice)</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
+          <t>noted</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(pending)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415__2026-12-16</t>
+          <t>tue-3414-a-practice-0945__2026-12-15</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>wed-3400-choir-1415</t>
+          <t>tue-3414-a-practice-0945</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28048,17 +28102,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>3400 (Choir)</t>
+          <t>3414-A (Practice)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -28066,12 +28120,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300__2026-12-16</t>
+          <t>wed-3400-choir-1415__2026-12-16</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>wed-3414-k-perc-1300</t>
+          <t>wed-3400-choir-1415</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -28081,27 +28135,35 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Moved to Mondays</t>
-        </is>
-      </c>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>3400 (Choir)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015__2026-12-16</t>
+          <t>wed-3414-k-perc-1300__2026-12-16</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>wed-3424-piano-lab-1015</t>
+          <t>wed-3414-k-perc-1300</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -28111,40 +28173,32 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>moved</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>3424 (Piano lab)</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
+          <t>cancelled</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Moved to Mondays</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945__2026-12-17</t>
+          <t>wed-3424-piano-lab-1015__2026-12-16</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>thu-3414-k-perc-0945</t>
+          <t>wed-3424-piano-lab-1015</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -28154,17 +28208,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>3416-D (Adjunct Office)</t>
+          <t>3424 (Piano lab)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
@@ -28172,40 +28226,78 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
+          <t>thu-3414-k-perc-0945__2026-12-17</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>thu-3414-k-perc-0945</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>moved</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>3416-D (Adjunct Office)</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
           <t>thu-3423-1315__2026-12-17</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>thu-3423-1315</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>moved</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>3422</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>13:15</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28327,7 +28419,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:20 UTC</t>
+          <t>2026-10-30 16:57 UTC</t>
         </is>
       </c>
     </row>
@@ -28350,7 +28442,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -28360,7 +28452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6">
